--- a/data/utilisateurmotsdepasse.xlsx
+++ b/data/utilisateurmotsdepasse.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="16">
   <si>
     <t>Hote</t>
   </si>
@@ -419,7 +419,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -496,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
@@ -519,7 +519,7 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
@@ -542,7 +542,7 @@
         <v>7</v>
       </c>
       <c r="C6" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
@@ -565,18 +565,41 @@
         <v>7</v>
       </c>
       <c r="C7" t="s">
+        <v>12</v>
+      </c>
+      <c r="D7" t="s">
+        <v>15</v>
+      </c>
+      <c r="E7" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" t="s">
+        <v>15</v>
+      </c>
+      <c r="G7" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8" s="1">
+        <v>6</v>
+      </c>
+      <c r="B8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C8" t="s">
         <v>13</v>
       </c>
-      <c r="D7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>14</v>
-      </c>
-      <c r="G7" t="s">
+      <c r="D8" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" t="s">
+        <v>14</v>
+      </c>
+      <c r="F8" t="s">
+        <v>14</v>
+      </c>
+      <c r="G8" t="s">
         <v>14</v>
       </c>
     </row>

--- a/data/utilisateurmotsdepasse.xlsx
+++ b/data/utilisateurmotsdepasse.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="17">
   <si>
     <t>Hote</t>
   </si>
@@ -44,6 +44,9 @@
   </si>
   <si>
     <t>debian-sys-maint</t>
+  </si>
+  <si>
+    <t>dondonserge</t>
   </si>
   <si>
     <t>mysql.infoschema</t>
@@ -419,7 +422,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -453,16 +456,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -476,16 +479,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G3" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -499,16 +502,16 @@
         <v>8</v>
       </c>
       <c r="D4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -522,16 +525,16 @@
         <v>10</v>
       </c>
       <c r="D5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -545,16 +548,16 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G6" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -568,16 +571,16 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="F7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G7" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -591,16 +594,39 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" t="s">
+        <v>16</v>
+      </c>
+      <c r="F8" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
+      <c r="A9" s="1">
+        <v>7</v>
+      </c>
+      <c r="B9" t="s">
+        <v>7</v>
+      </c>
+      <c r="C9" t="s">
         <v>14</v>
       </c>
-      <c r="E8" t="s">
-        <v>14</v>
-      </c>
-      <c r="F8" t="s">
-        <v>14</v>
-      </c>
-      <c r="G8" t="s">
-        <v>14</v>
+      <c r="D9" t="s">
+        <v>15</v>
+      </c>
+      <c r="E9" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/data/utilisateurmotsdepasse.xlsx
+++ b/data/utilisateurmotsdepasse.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="19">
   <si>
     <t>Hote</t>
   </si>
@@ -43,7 +43,13 @@
     <t>dondonedmond</t>
   </si>
   <si>
+    <t>administrateur</t>
+  </si>
+  <si>
     <t>debian-sys-maint</t>
+  </si>
+  <si>
+    <t>dondonlukas</t>
   </si>
   <si>
     <t>dondonserge</t>
@@ -422,7 +428,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:7">
@@ -456,16 +462,16 @@
         <v>8</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="E2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="F2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G2" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -479,16 +485,16 @@
         <v>9</v>
       </c>
       <c r="D3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="G3" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -499,19 +505,19 @@
         <v>7</v>
       </c>
       <c r="C4" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G4" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -522,19 +528,19 @@
         <v>7</v>
       </c>
       <c r="C5" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G5" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -548,16 +554,16 @@
         <v>11</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G6" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -571,16 +577,16 @@
         <v>12</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G7" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -594,16 +600,16 @@
         <v>13</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="E8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="F8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="G8" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -617,16 +623,62 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" t="s">
+        <v>18</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
+      <c r="A10" s="1">
+        <v>8</v>
+      </c>
+      <c r="B10" t="s">
+        <v>7</v>
+      </c>
+      <c r="C10" t="s">
         <v>15</v>
       </c>
-      <c r="E9" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" t="s">
-        <v>15</v>
-      </c>
-      <c r="G9" t="s">
-        <v>15</v>
+      <c r="D10" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
+      <c r="A11" s="1">
+        <v>9</v>
+      </c>
+      <c r="B11" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" t="s">
+        <v>17</v>
+      </c>
+      <c r="E11" t="s">
+        <v>17</v>
+      </c>
+      <c r="F11" t="s">
+        <v>17</v>
+      </c>
+      <c r="G11" t="s">
+        <v>17</v>
       </c>
     </row>
   </sheetData>
